--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104477_W3.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104477_W3.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.0623</v>
+        <v>5.4659</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9873</v>
+        <v>5.2668</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0751</v>
+        <v>0.1991</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7301</v>
+        <v>0.7351</v>
       </c>
       <c r="H2" t="n">
-        <v>1.4978</v>
+        <v>1.4991</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7675999999999999</v>
+        <v>-0.764</v>
       </c>
       <c r="J2" t="n">
-        <v>2.4563</v>
+        <v>2.44</v>
       </c>
       <c r="K2" t="n">
-        <v>2.459</v>
+        <v>2.4476</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.0027</v>
+        <v>-0.0077</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.7261</v>
+        <v>-1.7048</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.9485</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.7649</v>
+        <v>-0.7563</v>
       </c>
       <c r="P2" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1461</v>
+        <v>0.2543</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.747</v>
+        <v>-0.4416</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6009</v>
+        <v>0.6959</v>
       </c>
       <c r="V2" t="n">
-        <v>3.1173</v>
+        <v>3.1107</v>
       </c>
       <c r="W2" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>H. BENITEZ</t>
+          <t>L. OLINDE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2263</v>
+        <v>2.3332</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1077</v>
+        <v>2.2639</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1186</v>
+        <v>0.0693</v>
       </c>
       <c r="G3" t="n">
-        <v>2.2427</v>
+        <v>4.0508</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.6996</v>
+        <v>0.5712</v>
       </c>
       <c r="I3" t="n">
-        <v>3.9423</v>
+        <v>3.4797</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1579</v>
+        <v>4.566</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.3921</v>
+        <v>1.7064</v>
       </c>
       <c r="L3" t="n">
-        <v>4.5499</v>
+        <v>2.8596</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.9152</v>
+        <v>-0.5152</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.3075</v>
+        <v>-1.1353</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6077</v>
+        <v>0.6201</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.6805</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5878</v>
+        <v>1.3658</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2786</v>
+        <v>0.2823</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0575</v>
+        <v>-0.0258</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2211</v>
+        <v>0.3082</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3856</v>
+        <v>-1.0895</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.2249</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. OLINDE</t>
+          <t>H. BENITEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.803</v>
+        <v>2.2769</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7965</v>
+        <v>1.8428</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0065</v>
+        <v>0.4341</v>
       </c>
       <c r="G4" t="n">
-        <v>4.0452</v>
+        <v>2.2257</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5641</v>
+        <v>-1.7111</v>
       </c>
       <c r="I4" t="n">
-        <v>3.4812</v>
+        <v>3.9368</v>
       </c>
       <c r="J4" t="n">
-        <v>4.585</v>
+        <v>4.1173</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7144</v>
+        <v>-0.4179</v>
       </c>
       <c r="L4" t="n">
-        <v>2.8707</v>
+        <v>4.5352</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5397999999999999</v>
+        <v>-1.8916</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1503</v>
+        <v>-1.2932</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6105</v>
+        <v>-0.5984</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.9073</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R4" t="n">
-        <v>1.361</v>
+        <v>1.5934</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2423</v>
+        <v>0.3472</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5202</v>
+        <v>-0.156</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2779</v>
+        <v>0.5032</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.0927</v>
+        <v>0.387</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0927</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2981</v>
+        <v>1.4342</v>
       </c>
       <c r="E5" t="n">
-        <v>2.8429</v>
+        <v>2.723</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.5447</v>
+        <v>-1.2888</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.9004</v>
+        <v>-1.8914</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4718</v>
+        <v>-0.4738</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.4286</v>
+        <v>-1.4176</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4575</v>
+        <v>0.4423</v>
       </c>
       <c r="K5" t="n">
-        <v>0.159</v>
+        <v>0.1444</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2985</v>
+        <v>0.2979</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.3579</v>
+        <v>-2.3337</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6308</v>
+        <v>-0.6182</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.7272</v>
+        <v>-1.7155</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2531</v>
+        <v>-0.1312</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0393</v>
+        <v>-0.0561</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2925</v>
+        <v>-0.0752</v>
       </c>
       <c r="V5" t="n">
-        <v>1.8639</v>
+        <v>1.8634</v>
       </c>
       <c r="W5" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.4822</v>
+        <v>-0.4733</v>
       </c>
     </row>
     <row r="6">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1654</v>
+        <v>-0.1257</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1608</v>
+        <v>-0.0158</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3262</v>
+        <v>-0.1098</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.9692</v>
+        <v>-1.9582</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2725</v>
+        <v>0.2837</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.2417</v>
+        <v>-2.2419</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3997</v>
+        <v>0.3887</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0693</v>
+        <v>0.0689</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3304</v>
+        <v>0.3198</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.3689</v>
+        <v>-2.3469</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2033</v>
+        <v>0.2148</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.5721</v>
+        <v>-2.5617</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0109</v>
+        <v>0.0115</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2389</v>
+        <v>-0.4046</v>
       </c>
       <c r="U6" t="n">
-        <v>0.228</v>
+        <v>0.416</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.0279</v>
+        <v>-2.0435</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.1208</v>
+        <v>-1.6632</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0929</v>
+        <v>-0.3803</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4741</v>
+        <v>-0.4723</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3736</v>
+        <v>0.3816</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8477</v>
+        <v>-0.8538</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3216</v>
+        <v>1.3023</v>
       </c>
       <c r="K7" t="n">
-        <v>0.658</v>
+        <v>0.655</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6636</v>
+        <v>0.6473</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.7957</v>
+        <v>-1.7745</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2844</v>
+        <v>-0.2734</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.5113</v>
+        <v>-1.5011</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R7" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0587</v>
+        <v>-0.0673</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.747</v>
+        <v>-0.2535</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6883</v>
+        <v>0.1862</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W7" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.2212</v>
+        <v>-2.3951</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7603</v>
+        <v>-1.9622</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4609</v>
+        <v>-0.4329</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2789</v>
+        <v>0.2773</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7935</v>
+        <v>0.8036</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5145</v>
+        <v>-0.5264</v>
       </c>
       <c r="J8" t="n">
-        <v>1.6028</v>
+        <v>1.578</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6061</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9967</v>
+        <v>0.9747</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3239</v>
+        <v>-1.3007</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1874</v>
+        <v>0.2003</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.5113</v>
+        <v>-1.5011</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1391</v>
+        <v>-0.3066</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0393</v>
+        <v>-0.1258</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1785</v>
+        <v>-0.1808</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.1216</v>
+        <v>-2.5013</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2022</v>
+        <v>-1.9232</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9194</v>
+        <v>-0.5780999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.7654</v>
+        <v>-3.772</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.0563</v>
+        <v>-3.0505</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7091</v>
+        <v>-0.7215</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.5943</v>
+        <v>-1.621</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.4342</v>
+        <v>-1.4414</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1601</v>
+        <v>-0.1796</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.1711</v>
+        <v>-2.151</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.6221</v>
+        <v>-1.6091</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.549</v>
+        <v>-0.5419</v>
       </c>
       <c r="P9" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3297</v>
+        <v>0.2903</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6079</v>
+        <v>-0.3022</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2782</v>
+        <v>0.5925</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.7502</v>
+        <v>-5.6315</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.7087</v>
+        <v>-4.1416</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0415</v>
+        <v>-1.4899</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.174</v>
+        <v>-2.1786</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.3851</v>
+        <v>-1.3953</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7889</v>
+        <v>-0.7833</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3969</v>
+        <v>-0.4156</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.4715</v>
+        <v>-0.4901</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.7771</v>
+        <v>-1.7629</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9135</v>
+        <v>-0.9052</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8636</v>
+        <v>-0.8578</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S10" t="n">
-        <v>1.2385</v>
+        <v>0.3681</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0907</v>
+        <v>-0.3115</v>
       </c>
       <c r="U10" t="n">
-        <v>1.1478</v>
+        <v>0.6796</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.5099</v>
+        <v>-6.1805</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.1598</v>
+        <v>-5.698</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.35</v>
+        <v>-0.4825</v>
       </c>
       <c r="G11" t="n">
-        <v>-6.8475</v>
+        <v>-6.8532</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.5769</v>
+        <v>-3.5867</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.2706</v>
+        <v>-3.2665</v>
       </c>
       <c r="J11" t="n">
-        <v>-5.214</v>
+        <v>-5.2379</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.8279</v>
+        <v>-3.8448</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.3861</v>
+        <v>-1.3931</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.6335</v>
+        <v>-1.6154</v>
       </c>
       <c r="N11" t="n">
-        <v>0.251</v>
+        <v>0.2581</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.8844</v>
+        <v>-1.8734</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5943000000000001</v>
+        <v>-0.2589</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9043</v>
+        <v>-0.4114</v>
       </c>
       <c r="U11" t="n">
-        <v>0.31</v>
+        <v>0.1524</v>
       </c>
       <c r="V11" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.406500000000001</v>
+        <v>-7.367399999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.056599999999998</v>
+        <v>-3.307500000000002</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.3496</v>
+        <v>-4.0598</v>
       </c>
       <c r="G12" t="n">
-        <v>-9.8337</v>
+        <v>-9.8368</v>
       </c>
       <c r="H12" t="n">
-        <v>-6.6882</v>
+        <v>-6.6782</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.1452</v>
+        <v>-3.158500000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>7.775600000000001</v>
+        <v>7.5601</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.4599000000000002</v>
+        <v>-0.5686</v>
       </c>
       <c r="L12" t="n">
-        <v>8.2355</v>
+        <v>8.1286</v>
       </c>
       <c r="M12" t="n">
-        <v>-17.6092</v>
+        <v>-17.3967</v>
       </c>
       <c r="N12" t="n">
-        <v>-6.2281</v>
+        <v>-6.1097</v>
       </c>
       <c r="O12" t="n">
-        <v>-11.381</v>
+        <v>-11.2871</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q12" t="n">
-        <v>-15.8783</v>
+        <v>-15.9343</v>
       </c>
       <c r="R12" t="n">
-        <v>13.61</v>
+        <v>13.658</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2571000000000001</v>
+        <v>0.7897</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.5385</v>
+        <v>-2.4885</v>
       </c>
       <c r="U12" t="n">
-        <v>3.2812</v>
+        <v>3.278</v>
       </c>
       <c r="V12" t="n">
-        <v>3.952700000000001</v>
+        <v>3.956</v>
       </c>
       <c r="W12" t="n">
-        <v>7.584599999999999</v>
+        <v>7.5549</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.6318</v>
+        <v>-3.598999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.7349</v>
+        <v>5.1132</v>
       </c>
       <c r="E13" t="n">
-        <v>2.715</v>
+        <v>2.7762</v>
       </c>
       <c r="F13" t="n">
-        <v>2.0199</v>
+        <v>2.337</v>
       </c>
       <c r="G13" t="n">
-        <v>1.1417</v>
+        <v>1.1304</v>
       </c>
       <c r="H13" t="n">
-        <v>3.41</v>
+        <v>3.3929</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.2683</v>
+        <v>-2.2625</v>
       </c>
       <c r="J13" t="n">
-        <v>1.9937</v>
+        <v>1.9574</v>
       </c>
       <c r="K13" t="n">
-        <v>3.3799</v>
+        <v>3.3505</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.3861</v>
+        <v>-1.3931</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.8521</v>
+        <v>-0.827</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0301</v>
+        <v>0.0424</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.8822</v>
+        <v>-0.8694</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R13" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2311</v>
+        <v>0.1696</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8347</v>
+        <v>-0.718</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6037</v>
+        <v>0.8875999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>3.8243</v>
+        <v>3.8132</v>
       </c>
       <c r="W13" t="n">
-        <v>3.8243</v>
+        <v>3.8132</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.1955</v>
+        <v>3.8067</v>
       </c>
       <c r="E14" t="n">
-        <v>4.2955</v>
+        <v>4.1449</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1001</v>
+        <v>-0.3382</v>
       </c>
       <c r="G14" t="n">
-        <v>3.1711</v>
+        <v>3.1727</v>
       </c>
       <c r="H14" t="n">
-        <v>3.8801</v>
+        <v>3.8802</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.709</v>
+        <v>-0.7075</v>
       </c>
       <c r="J14" t="n">
-        <v>4.844</v>
+        <v>4.8153</v>
       </c>
       <c r="K14" t="n">
-        <v>3.3941</v>
+        <v>3.3784</v>
       </c>
       <c r="L14" t="n">
-        <v>1.4499</v>
+        <v>1.4369</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.6729</v>
+        <v>-1.6426</v>
       </c>
       <c r="N14" t="n">
-        <v>0.486</v>
+        <v>0.5018</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.159</v>
+        <v>-2.1444</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R14" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5634</v>
+        <v>0.0406</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0393</v>
+        <v>-0.077</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6028</v>
+        <v>0.1176</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. TOBEY</t>
+          <t>E. VILA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0338</v>
+        <v>2.0129</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0775</v>
+        <v>1.3816</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1113</v>
+        <v>0.6313</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2061</v>
+        <v>1.5054</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5398</v>
+        <v>0.0056</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.7459</v>
+        <v>1.4998</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9923</v>
+        <v>1.5908</v>
       </c>
       <c r="K15" t="n">
-        <v>1.856</v>
+        <v>0.0345</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.8637</v>
+        <v>1.5563</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.1984</v>
+        <v>-0.0854</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3162</v>
+        <v>-0.0289</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8822</v>
+        <v>-0.0565</v>
       </c>
       <c r="P15" t="n">
-        <v>1.361</v>
+        <v>0.4553</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.4952</v>
+        <v>0.4553</v>
       </c>
       <c r="S15" t="n">
-        <v>1.6501</v>
+        <v>0.0523</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2571</v>
+        <v>-0.2091</v>
       </c>
       <c r="U15" t="n">
-        <v>1.9072</v>
+        <v>0.2614</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.7712</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.3214</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. VILA</t>
+          <t>A. ALBICY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8581</v>
+        <v>1.7695</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3905</v>
+        <v>0.9413</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4676</v>
+        <v>0.8282</v>
       </c>
       <c r="G16" t="n">
-        <v>1.5088</v>
+        <v>3.218</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0028</v>
+        <v>0.7719</v>
       </c>
       <c r="I16" t="n">
-        <v>1.506</v>
+        <v>2.446</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5992</v>
+        <v>4.6606</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0346</v>
+        <v>0.7584</v>
       </c>
       <c r="L16" t="n">
-        <v>1.5646</v>
+        <v>3.9022</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.09039999999999999</v>
+        <v>-1.4426</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0318</v>
+        <v>0.0135</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0586</v>
+        <v>-1.4562</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4537</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-3.4145</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4537</v>
+        <v>1.8211</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1043</v>
+        <v>-0.0128</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2087</v>
+        <v>-0.4626</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1043</v>
+        <v>0.4498</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. SALVO</t>
+          <t>M. TOBEY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.796</v>
+        <v>1.1811</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.1465</v>
+        <v>-0.472</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9426</v>
+        <v>1.6532</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.7887</v>
+        <v>-0.2099</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.9162</v>
+        <v>1.5313</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1275</v>
+        <v>-1.7412</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.981</v>
+        <v>0.9618</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.5381</v>
+        <v>1.8336</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5570000000000001</v>
+        <v>-0.8718</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1923</v>
+        <v>-1.1717</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3781</v>
+        <v>-0.3023</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5705</v>
+        <v>-0.8694</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4537</v>
+        <v>1.3658</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4537</v>
+        <v>2.5039</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8096</v>
+        <v>0.7991</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4869</v>
+        <v>-0.6112</v>
       </c>
       <c r="U17" t="n">
-        <v>1.2966</v>
+        <v>1.4104</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3214</v>
+        <v>-0.7739</v>
       </c>
       <c r="W17" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. ALBICY</t>
+          <t>P. PELOS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7839</v>
+        <v>1.0593</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6191</v>
+        <v>2.1809</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1648</v>
+        <v>-1.1216</v>
       </c>
       <c r="G18" t="n">
-        <v>3.2046</v>
+        <v>1.8454</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7602</v>
+        <v>0.4766</v>
       </c>
       <c r="I18" t="n">
-        <v>2.4443</v>
+        <v>1.3688</v>
       </c>
       <c r="J18" t="n">
-        <v>4.6775</v>
+        <v>3.4331</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7619</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>3.9156</v>
+        <v>3.3436</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4729</v>
+        <v>-1.5877</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0017</v>
+        <v>0.3871</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.4712</v>
+        <v>-1.9749</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.5878</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.4025</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8147</v>
+        <v>1.1382</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9935</v>
+        <v>-0.08359999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8166</v>
+        <v>-0.1141</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1769</v>
+        <v>0.0305</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1607</v>
+        <v>-0.7025</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. PELOS</t>
+          <t>M. SALVO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7645</v>
+        <v>0.3746</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8497</v>
+        <v>-1.0479</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0852</v>
+        <v>1.4225</v>
       </c>
       <c r="G19" t="n">
-        <v>1.8459</v>
+        <v>-0.7923</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4732</v>
+        <v>-1.9184</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3727</v>
+        <v>1.1261</v>
       </c>
       <c r="J19" t="n">
-        <v>3.4526</v>
+        <v>-0.9939</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0968</v>
+        <v>-1.5448</v>
       </c>
       <c r="L19" t="n">
-        <v>3.3558</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6066</v>
+        <v>0.2016</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3764</v>
+        <v>-0.3736</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.9831</v>
+        <v>0.5752</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.4553</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1342</v>
+        <v>0.4553</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3744</v>
+        <v>0.3962</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4688</v>
+        <v>-0.3695</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0944</v>
+        <v>0.7655999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.7071</v>
+        <v>0.3155</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.7071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,22 +1969,22 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1891</v>
+        <v>0.2234</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0696</v>
+        <v>-0.0697</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2586</v>
+        <v>0.2931</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0586</v>
+        <v>-0.0565</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0586</v>
+        <v>-0.0565</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1996,31 +1996,31 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0586</v>
+        <v>-0.0565</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0586</v>
+        <v>-0.0565</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0209</v>
+        <v>0.0523</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0696</v>
+        <v>-0.0697</v>
       </c>
       <c r="U20" t="n">
-        <v>0.09039999999999999</v>
+        <v>0.122</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5163</v>
+        <v>-0.2288</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4158</v>
+        <v>0.5319</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9321</v>
+        <v>-0.7607</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6146</v>
+        <v>0.6201</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1717</v>
+        <v>-0.1696</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7864</v>
+        <v>0.7896</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7637</v>
+        <v>0.762</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7463</v>
+        <v>0.7447</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.149</v>
+        <v>-0.1419</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1891</v>
+        <v>-0.1868</v>
       </c>
       <c r="O21" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3312</v>
+        <v>-0.0569</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3478</v>
+        <v>-0.2301</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0166</v>
+        <v>0.1732</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="22">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2221</v>
+        <v>-1.0443</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.1891</v>
+        <v>-3.329</v>
       </c>
       <c r="F22" t="n">
-        <v>1.967</v>
+        <v>2.2847</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.185</v>
+        <v>-0.1694</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0014</v>
+        <v>0.0028</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1865</v>
+        <v>-0.1722</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1193</v>
+        <v>-0.132</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.3432</v>
+        <v>-0.3555</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2239</v>
+        <v>0.2234</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.06569999999999999</v>
+        <v>-0.0373</v>
       </c>
       <c r="N22" t="n">
-        <v>0.3446</v>
+        <v>0.3583</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4104</v>
+        <v>-0.3956</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R22" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1878</v>
+        <v>0.3542</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0302</v>
+        <v>-0.1467</v>
       </c>
       <c r="U22" t="n">
-        <v>0.218</v>
+        <v>0.501</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.5291</v>
+        <v>-1.6492</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0187</v>
+        <v>-0.131</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.5478</v>
+        <v>-1.5181</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3946</v>
+        <v>0.3847</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1255</v>
+        <v>0.129</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2691</v>
+        <v>0.2556</v>
       </c>
       <c r="J23" t="n">
-        <v>1.1135</v>
+        <v>1.0842</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0795</v>
+        <v>0.0722</v>
       </c>
       <c r="L23" t="n">
-        <v>1.034</v>
+        <v>1.012</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.7189</v>
+        <v>-0.6995</v>
       </c>
       <c r="N23" t="n">
-        <v>0.046</v>
+        <v>0.0568</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.7649</v>
+        <v>-0.7563</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2616</v>
+        <v>0.1451</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0393</v>
+        <v>-0.077</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2223</v>
+        <v>0.2221</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.6819</v>
+        <v>-2.6262</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.472</v>
+        <v>-2.8475</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2099</v>
+        <v>0.2212</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.8091</v>
+        <v>-0.8117</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.4169</v>
+        <v>-1.4242</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6078</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.7269</v>
+        <v>-0.7423</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.5106</v>
+        <v>-1.5243</v>
       </c>
       <c r="L24" t="n">
-        <v>0.7837</v>
+        <v>0.782</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.0822</v>
+        <v>-0.0694</v>
       </c>
       <c r="N24" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.1002</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.1759</v>
+        <v>-0.1695</v>
       </c>
       <c r="P24" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R24" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.075</v>
+        <v>-0.021</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1603</v>
+        <v>-0.193</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2353</v>
+        <v>0.1721</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.0246</v>
+        <v>-2.0212</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>8.4064</v>
+        <v>9.9922</v>
       </c>
       <c r="E25" t="n">
-        <v>4.349600000000001</v>
+        <v>4.059699999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>4.056699999999998</v>
+        <v>5.932600000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>9.833799999999998</v>
+        <v>9.8369</v>
       </c>
       <c r="H25" t="n">
-        <v>6.6882</v>
+        <v>6.6781</v>
       </c>
       <c r="I25" t="n">
-        <v>3.1455</v>
+        <v>3.1584</v>
       </c>
       <c r="J25" t="n">
-        <v>17.6093</v>
+        <v>17.397</v>
       </c>
       <c r="K25" t="n">
-        <v>6.228199999999999</v>
+        <v>6.109599999999998</v>
       </c>
       <c r="L25" t="n">
-        <v>11.381</v>
+        <v>11.2871</v>
       </c>
       <c r="M25" t="n">
-        <v>-7.775399999999999</v>
+        <v>-7.56</v>
       </c>
       <c r="N25" t="n">
-        <v>0.4599000000000001</v>
+        <v>0.5685000000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>-8.235600000000002</v>
+        <v>-8.128599999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>2.2684</v>
+        <v>2.2764</v>
       </c>
       <c r="Q25" t="n">
-        <v>-13.6101</v>
+        <v>-13.6581</v>
       </c>
       <c r="R25" t="n">
-        <v>15.8785</v>
+        <v>15.9344</v>
       </c>
       <c r="S25" t="n">
-        <v>0.2570999999999997</v>
+        <v>1.8351</v>
       </c>
       <c r="T25" t="n">
-        <v>-3.2815</v>
+        <v>-3.278</v>
       </c>
       <c r="U25" t="n">
-        <v>3.5385</v>
+        <v>5.113300000000001</v>
       </c>
       <c r="V25" t="n">
-        <v>-3.9527</v>
+        <v>-3.9558</v>
       </c>
       <c r="W25" t="n">
-        <v>3.631699999999999</v>
+        <v>3.5989</v>
       </c>
       <c r="X25" t="n">
-        <v>-7.5846</v>
+        <v>-7.554800000000001</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104477_W3.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104477_W3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104477_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104477_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104477_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.4733</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104477_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104477_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104477_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104477_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104477_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104477_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104477_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-3.598999999999999</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104477_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104477_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104477_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104477_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104477_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104477_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104477_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104477_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104477_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104477_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104477_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104477_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-7.554800000000001</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
